--- a/0_data/three_challenges_codebook.xlsx
+++ b/0_data/three_challenges_codebook.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Clemens Lindner\Documents\github\bigot_and_tolerant_personalites\0_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Clemens Lindner\Documents\GitHub\bigot_and_tolerant_personalites\0_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A66987F3-87FD-4AD9-AD2D-863785AC12F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8460D08D-A1F1-41E0-A7FE-C45211640101}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-2025" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{5059903E-ADBB-4520-B1A6-60D4EA1E22CC}"/>
+    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="11440" xr2:uid="{5059903E-ADBB-4520-B1A6-60D4EA1E22CC}"/>
   </bookViews>
   <sheets>
     <sheet name="Study 1a" sheetId="1" r:id="rId1"/>
@@ -34,12 +34,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1603" uniqueCount="726">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1626" uniqueCount="711">
   <si>
     <t>variable</t>
   </si>
@@ -1874,24 +1877,6 @@
     <t>Important to live in secure and safe surroundings</t>
   </si>
   <si>
-    <t>hrshsnt</t>
-  </si>
-  <si>
-    <t>People who break the law much harsher sentences</t>
-  </si>
-  <si>
-    <t>imdfetn</t>
-  </si>
-  <si>
-    <t>Allow many/few immigrants of different race/ethnic group from majority</t>
-  </si>
-  <si>
-    <t>impcntr</t>
-  </si>
-  <si>
-    <t>Allow many/few immigrants from poorer countries outside Europe</t>
-  </si>
-  <si>
     <t>imbgeco</t>
   </si>
   <si>
@@ -2049,9 +2034,6 @@
     </r>
   </si>
   <si>
-    <t>Prejudice_gays</t>
-  </si>
-  <si>
     <t>Prejudice_women</t>
   </si>
   <si>
@@ -2061,9 +2043,6 @@
     <t>Prejudice_unemployed</t>
   </si>
   <si>
-    <t>Prejudice_age</t>
-  </si>
-  <si>
     <t>response_scale</t>
   </si>
   <si>
@@ -2523,9 +2502,6 @@
     <t>trad_5</t>
   </si>
   <si>
-    <t>trad_6</t>
-  </si>
-  <si>
     <t>prj_immi_1</t>
   </si>
   <si>
@@ -2535,12 +2511,6 @@
     <t>prj_immi_3</t>
   </si>
   <si>
-    <t>prj_immi_4</t>
-  </si>
-  <si>
-    <t>prj_immi_5</t>
-  </si>
-  <si>
     <t>prj_gay_1</t>
   </si>
   <si>
@@ -2559,127 +2529,115 @@
     <t>prj_age70</t>
   </si>
   <si>
-    <t>ess4</t>
-  </si>
-  <si>
-    <t>ess7</t>
-  </si>
-  <si>
-    <t>ess8</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
     <t>ess_variable_name</t>
   </si>
   <si>
-    <t>Prejudice_jews</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>prj_jews</t>
-  </si>
-  <si>
-    <t>aljewlv</t>
-  </si>
-  <si>
-    <t>Allow many or few Jewish people to come and live in country</t>
-  </si>
-  <si>
-    <t>Allow many or few Muslims to come and live in country</t>
-  </si>
-  <si>
-    <t>Prejudice_muslims</t>
-  </si>
-  <si>
-    <t>prj_muslms</t>
-  </si>
-  <si>
-    <t>almuslv</t>
-  </si>
-  <si>
-    <t>algyplv</t>
-  </si>
-  <si>
-    <t>prj_sinti</t>
-  </si>
-  <si>
-    <t>Prejudice_sinti_roma</t>
-  </si>
-  <si>
-    <t>Allow many or few Gypsies to come and live in country</t>
-  </si>
-  <si>
-    <t>alpfpe</t>
-  </si>
-  <si>
-    <t>Allow professionals from [poor European country providing largest number of migrants]</t>
-  </si>
-  <si>
-    <t>Prejudice_poorer_countries</t>
-  </si>
-  <si>
-    <t>Allow professionals from [poor non-European country providing largest number of migrants]</t>
-  </si>
-  <si>
-    <t>alpfpne</t>
-  </si>
-  <si>
-    <t>prj_prf_poor_2</t>
-  </si>
-  <si>
-    <t>prj_prf_poor_1</t>
-  </si>
-  <si>
-    <t>Allow unskilled labourers from [poor European country providing largest number of migrants]</t>
-  </si>
-  <si>
-    <t>allbpe</t>
-  </si>
-  <si>
-    <t>prj_unsk_poor_1</t>
-  </si>
-  <si>
-    <t>Allow unskilled labourers from [poor non-European country providing largest number of migrants]</t>
-  </si>
-  <si>
-    <t>allbpne</t>
-  </si>
-  <si>
-    <t>prj_unsk_poor_2</t>
-  </si>
-  <si>
-    <t>gvslvue</t>
-  </si>
-  <si>
-    <t>prj_unempl_2</t>
-  </si>
-  <si>
-    <t>dfincac</t>
-  </si>
-  <si>
-    <t>prj_unempl_3</t>
-  </si>
-  <si>
-    <t>bennent</t>
-  </si>
-  <si>
-    <t>prj_unempl_4</t>
-  </si>
-  <si>
-    <t>sblazy</t>
-  </si>
-  <si>
-    <t>prj_unempl_5</t>
-  </si>
-  <si>
-    <t>sbbsntx</t>
-  </si>
-  <si>
-    <t>prj_unempl_6</t>
+    <t>full_item</t>
+  </si>
+  <si>
+    <t>short_item</t>
+  </si>
+  <si>
+    <t>Now I will briefly describe some people. Please listen to each description and tell me how much each person is or is not like you. Use this card for your answer.</t>
+  </si>
+  <si>
+    <t>She/he believes that people should do what they're told. She/he thinks people should follow rules at all times, even when no-one is watching.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> It is important to her/him that the government ensures her/his safety against all threats. She/he wants the state to be strong so it can defend its citizens.</t>
+  </si>
+  <si>
+    <t>It is important to her/him always to behave properly. She/he wants to avoid doing anything people would say is wrong.</t>
+  </si>
+  <si>
+    <t>Tradition is important to her/him. She/he tries to follow the customs handed down by her/his religion or her/his family.</t>
+  </si>
+  <si>
+    <t>It is important to her/him to live in secure surroundings. She/he avoids anything that might endanger her/his safety.</t>
+  </si>
+  <si>
+    <t>Would you say it is generally bad or good for [country]'s economy that people come to live here from other countries?</t>
+  </si>
+  <si>
+    <t>And, using this card, would you say that [country]'s cultural life is generally undermined or enriched by people coming to live here from other countries?</t>
+  </si>
+  <si>
+    <t>Is [country] made a worse or a better place to live by people coming to live here from other countries?</t>
+  </si>
+  <si>
+    <t>Using this card, please say to what extent you agree or disagree with each of the following statements. Gay men and lesbians should be free to live their own life as they wish</t>
+  </si>
+  <si>
+    <t>introduction</t>
+  </si>
+  <si>
+    <t>Using this card, please say how much you agree or disagree with each of the following statements. A woman should be prepared to cut down on her paid work for the sake of her family.</t>
+  </si>
+  <si>
+    <t>1 = Agree strongly, 2 = Agree, 3 = Neither agree nor disagree, 4 = Disagree, 5 = Disagree strongly</t>
+  </si>
+  <si>
+    <t>Using this card, please say to what extent you agree or disagree with each of the following statements. When jobs are scarce, men should have more right to a job than women.</t>
+  </si>
+  <si>
+    <t>Using this card, please say how much you agree or disagree with each of the following statements about people in [country]. Most unemployed people do not really try to find a job.</t>
+  </si>
+  <si>
+    <t>Using this card, tell me overall how negative or positive you feel towards people in their 20s? Please tell me on a score of 0 to 10, where 0 means extremely negative and 10 means extremely positive.</t>
+  </si>
+  <si>
+    <t>0 = Extremely negative, 10 = Extremely positive</t>
+  </si>
+  <si>
+    <t>And overall, how negative or positive do you feel towards people over 70?</t>
+  </si>
+  <si>
+    <t>0 = Bad for the economy, 10 = Good for the economy</t>
+  </si>
+  <si>
+    <t>0 = Cultural life undermined, 10 = Cultural life enriched</t>
+  </si>
+  <si>
+    <t>0 = Worse place to live, 10 = Better place to live</t>
+  </si>
+  <si>
+    <t>1 = Very much like me, 2 = Like me, 3 = Somewhat like me, 4 = A little like me, 5 = Not like me, 6 = Not like me at all</t>
+  </si>
+  <si>
+    <t>Prejudice_gay_people</t>
+  </si>
+  <si>
+    <t>Prejudice_age_20s</t>
+  </si>
+  <si>
+    <t>Prejudice_age_over_70</t>
+  </si>
+  <si>
+    <t>prj_gay_2</t>
+  </si>
+  <si>
+    <t>prj_gay_3</t>
+  </si>
+  <si>
+    <t>Using this card, please say to what extent you agree or disagree with each of the following statements.</t>
+  </si>
+  <si>
+    <t>Gay men and lesbians should be free to live their own life as they wish.</t>
+  </si>
+  <si>
+    <t>If a close family member was a gay man or a lesbian, I would feel ashamed.</t>
+  </si>
+  <si>
+    <t>Gay male and lesbian couples should have the same rights to adopt children as straight couples.</t>
+  </si>
+  <si>
+    <t>fct_coding</t>
+  </si>
+  <si>
+    <t>1 = female, 2 = male, 3 = other, 4 = NA</t>
+  </si>
+  <si>
+    <t>1 = isced_1, 2 = isced_2, 3 = isced_2, 4 = isced_3, 5 = isced_4, 6 = isced_6, 7 = isced_7</t>
   </si>
 </sst>
 </file>
@@ -3070,7 +3028,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{019B6BE1-EFDB-4B9D-AE74-42886FDB1FDE}">
-  <dimension ref="A1:G132"/>
+  <dimension ref="A1:H132"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="3" width="13.453125" customWidth="1"/>
@@ -3080,12 +3038,12 @@
     <col min="7" max="7" width="28.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="C1" t="s">
         <v>140</v>
@@ -3102,13 +3060,16 @@
       <c r="G1" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="F2" t="s">
         <v>134</v>
@@ -3117,12 +3078,12 @@
         <v>375</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="F3" t="s">
         <v>367</v>
@@ -3131,12 +3092,12 @@
         <v>376</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="F4" t="s">
         <v>135</v>
@@ -3145,12 +3106,12 @@
         <v>377</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="F5" t="s">
         <v>136</v>
@@ -3159,12 +3120,12 @@
         <v>378</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="F6" t="s">
         <v>137</v>
@@ -3173,12 +3134,12 @@
         <v>379</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="C7" t="s">
         <v>141</v>
@@ -3193,12 +3154,12 @@
         <v>262</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="C8" t="s">
         <v>141</v>
@@ -3213,12 +3174,12 @@
         <v>263</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="C9" t="s">
         <v>141</v>
@@ -3233,12 +3194,12 @@
         <v>264</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="C10" t="s">
         <v>141</v>
@@ -3253,12 +3214,12 @@
         <v>265</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="C11" t="s">
         <v>141</v>
@@ -3273,12 +3234,12 @@
         <v>266</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="C12" t="s">
         <v>141</v>
@@ -3293,12 +3254,12 @@
         <v>267</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="C13" t="s">
         <v>141</v>
@@ -3313,12 +3274,12 @@
         <v>268</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="C14" t="s">
         <v>141</v>
@@ -3333,12 +3294,12 @@
         <v>269</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="C15" t="s">
         <v>141</v>
@@ -3353,12 +3314,12 @@
         <v>270</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="C16" t="s">
         <v>142</v>
@@ -3375,7 +3336,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="C17" t="s">
         <v>142</v>
@@ -3392,7 +3353,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="C18" t="s">
         <v>142</v>
@@ -3409,7 +3370,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="C19" t="s">
         <v>142</v>
@@ -3426,7 +3387,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="C20" t="s">
         <v>142</v>
@@ -3443,7 +3404,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="C21" t="s">
         <v>142</v>
@@ -3460,7 +3421,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>538</v>
+        <v>530</v>
       </c>
       <c r="C22" t="s">
         <v>142</v>
@@ -3477,7 +3438,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="C23" t="s">
         <v>142</v>
@@ -3494,7 +3455,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="C24" t="s">
         <v>142</v>
@@ -3514,7 +3475,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="C25" t="s">
         <v>142</v>
@@ -3534,7 +3495,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="C26" t="s">
         <v>142</v>
@@ -3554,7 +3515,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="C27" t="s">
         <v>142</v>
@@ -3574,7 +3535,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="C28" t="s">
         <v>142</v>
@@ -3594,7 +3555,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="C29" t="s">
         <v>142</v>
@@ -3614,7 +3575,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="C30" t="s">
         <v>142</v>
@@ -3634,7 +3595,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="C31" t="s">
         <v>142</v>
@@ -3654,7 +3615,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="C32" t="s">
         <v>166</v>
@@ -3671,7 +3632,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>549</v>
+        <v>541</v>
       </c>
       <c r="C33" t="s">
         <v>166</v>
@@ -3691,7 +3652,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="C34" t="s">
         <v>166</v>
@@ -3708,7 +3669,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>551</v>
+        <v>543</v>
       </c>
       <c r="C35" t="s">
         <v>166</v>
@@ -3728,7 +3689,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="C36" t="s">
         <v>166</v>
@@ -3745,7 +3706,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>553</v>
+        <v>545</v>
       </c>
       <c r="C37" t="s">
         <v>166</v>
@@ -3765,7 +3726,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="C38" t="s">
         <v>166</v>
@@ -3782,7 +3743,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="C39" t="s">
         <v>166</v>
@@ -3802,7 +3763,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="C40" t="s">
         <v>166</v>
@@ -3819,7 +3780,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="C41" t="s">
         <v>166</v>
@@ -3836,7 +3797,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>558</v>
+        <v>550</v>
       </c>
       <c r="C42" t="s">
         <v>166</v>
@@ -3856,7 +3817,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>559</v>
+        <v>551</v>
       </c>
       <c r="C43" t="s">
         <v>166</v>
@@ -3876,7 +3837,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>560</v>
+        <v>552</v>
       </c>
       <c r="C44" t="s">
         <v>166</v>
@@ -3896,7 +3857,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>561</v>
+        <v>553</v>
       </c>
       <c r="C45" t="s">
         <v>166</v>
@@ -3913,7 +3874,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="C46" t="s">
         <v>166</v>
@@ -3933,7 +3894,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="C47" t="s">
         <v>166</v>
@@ -3953,7 +3914,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="C48" t="s">
         <v>166</v>
@@ -3973,7 +3934,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>565</v>
+        <v>557</v>
       </c>
       <c r="C49" t="s">
         <v>166</v>
@@ -3993,7 +3954,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>566</v>
+        <v>558</v>
       </c>
       <c r="C50" t="s">
         <v>166</v>
@@ -4010,7 +3971,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="C51" t="s">
         <v>166</v>
@@ -4027,7 +3988,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="C52" t="s">
         <v>166</v>
@@ -4047,7 +4008,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="C53" t="s">
         <v>166</v>
@@ -4064,7 +4025,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="C54" t="s">
         <v>166</v>
@@ -4084,7 +4045,7 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="C55" t="s">
         <v>166</v>
@@ -4104,7 +4065,7 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>572</v>
+        <v>564</v>
       </c>
       <c r="C56" t="s">
         <v>166</v>
@@ -4121,7 +4082,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="C57" t="s">
         <v>166</v>
@@ -4138,7 +4099,7 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>574</v>
+        <v>566</v>
       </c>
       <c r="C58" t="s">
         <v>166</v>
@@ -4155,7 +4116,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>575</v>
+        <v>567</v>
       </c>
       <c r="C59" t="s">
         <v>166</v>
@@ -4175,7 +4136,7 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="C60" t="s">
         <v>166</v>
@@ -4195,7 +4156,7 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>577</v>
+        <v>569</v>
       </c>
       <c r="C61" t="s">
         <v>166</v>
@@ -4212,7 +4173,7 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="C62" t="s">
         <v>205</v>
@@ -4232,7 +4193,7 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="C63" t="s">
         <v>205</v>
@@ -4252,7 +4213,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>580</v>
+        <v>572</v>
       </c>
       <c r="C64" t="s">
         <v>205</v>
@@ -4275,7 +4236,7 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="C65" t="s">
         <v>205</v>
@@ -4298,7 +4259,7 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="C66" t="s">
         <v>205</v>
@@ -4318,7 +4279,7 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
       <c r="C67" t="s">
         <v>205</v>
@@ -4338,7 +4299,7 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="C68" t="s">
         <v>205</v>
@@ -4361,7 +4322,7 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>585</v>
+        <v>577</v>
       </c>
       <c r="C69" t="s">
         <v>205</v>
@@ -4384,7 +4345,7 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="C70" t="s">
         <v>206</v>
@@ -4404,7 +4365,7 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>591</v>
+        <v>583</v>
       </c>
       <c r="C71" t="s">
         <v>206</v>
@@ -4424,7 +4385,7 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="C72" t="s">
         <v>206</v>
@@ -4444,7 +4405,7 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
       <c r="C73" t="s">
         <v>206</v>
@@ -4464,7 +4425,7 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="C74" t="s">
         <v>206</v>
@@ -4484,7 +4445,7 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="C75" t="s">
         <v>206</v>
@@ -4504,7 +4465,7 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="C76" t="s">
         <v>206</v>
@@ -4524,7 +4485,7 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="C77" t="s">
         <v>206</v>
@@ -4544,7 +4505,7 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="C78" t="s">
         <v>206</v>
@@ -4564,7 +4525,7 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="C79" t="s">
         <v>206</v>
@@ -4584,7 +4545,7 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="C80" t="s">
         <v>206</v>
@@ -4604,7 +4565,7 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>601</v>
+        <v>593</v>
       </c>
       <c r="C81" t="s">
         <v>206</v>
@@ -4624,7 +4585,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="C82" t="s">
         <v>206</v>
@@ -4644,7 +4605,7 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="C83" t="s">
         <v>206</v>
@@ -4664,7 +4625,7 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="C84" t="s">
         <v>206</v>
@@ -4684,7 +4645,7 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="C85" t="s">
         <v>206</v>
@@ -4704,7 +4665,7 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="C86" t="s">
         <v>206</v>
@@ -4724,7 +4685,7 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="C87" t="s">
         <v>206</v>
@@ -4744,7 +4705,7 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="C88" t="s">
         <v>206</v>
@@ -4764,7 +4725,7 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="C89" t="s">
         <v>206</v>
@@ -4784,7 +4745,7 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="C90" t="s">
         <v>206</v>
@@ -4804,7 +4765,7 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="C91" t="s">
         <v>206</v>
@@ -4824,7 +4785,7 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="C92" t="s">
         <v>206</v>
@@ -4844,7 +4805,7 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="C93" t="s">
         <v>206</v>
@@ -4864,7 +4825,7 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="C94" t="s">
         <v>206</v>
@@ -4884,7 +4845,7 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="C95" t="s">
         <v>206</v>
@@ -4904,7 +4865,7 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="C96" t="s">
         <v>206</v>
@@ -4919,12 +4880,12 @@
         <v>346</v>
       </c>
     </row>
-    <row r="97" spans="1:7">
+    <row r="97" spans="1:8">
       <c r="A97" t="s">
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
       <c r="C97" t="s">
         <v>206</v>
@@ -4939,12 +4900,12 @@
         <v>359</v>
       </c>
     </row>
-    <row r="98" spans="1:7">
+    <row r="98" spans="1:8">
       <c r="A98" t="s">
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="C98" t="s">
         <v>206</v>
@@ -4959,12 +4920,12 @@
         <v>347</v>
       </c>
     </row>
-    <row r="99" spans="1:7">
+    <row r="99" spans="1:8">
       <c r="A99" t="s">
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
       <c r="C99" t="s">
         <v>206</v>
@@ -4979,12 +4940,12 @@
         <v>362</v>
       </c>
     </row>
-    <row r="100" spans="1:7">
+    <row r="100" spans="1:8">
       <c r="A100" t="s">
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="C100" t="s">
         <v>206</v>
@@ -4999,12 +4960,12 @@
         <v>325</v>
       </c>
     </row>
-    <row r="101" spans="1:7">
+    <row r="101" spans="1:8">
       <c r="A101" t="s">
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>621</v>
+        <v>613</v>
       </c>
       <c r="C101" t="s">
         <v>206</v>
@@ -5019,12 +4980,12 @@
         <v>326</v>
       </c>
     </row>
-    <row r="102" spans="1:7">
+    <row r="102" spans="1:8">
       <c r="A102" t="s">
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>622</v>
+        <v>614</v>
       </c>
       <c r="C102" t="s">
         <v>206</v>
@@ -5039,12 +5000,12 @@
         <v>333</v>
       </c>
     </row>
-    <row r="103" spans="1:7">
+    <row r="103" spans="1:8">
       <c r="A103" t="s">
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="C103" t="s">
         <v>206</v>
@@ -5059,12 +5020,12 @@
         <v>329</v>
       </c>
     </row>
-    <row r="104" spans="1:7">
+    <row r="104" spans="1:8">
       <c r="A104" t="s">
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>624</v>
+        <v>616</v>
       </c>
       <c r="C104" t="s">
         <v>206</v>
@@ -5079,12 +5040,12 @@
         <v>327</v>
       </c>
     </row>
-    <row r="105" spans="1:7">
+    <row r="105" spans="1:8">
       <c r="A105" t="s">
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="C105" t="s">
         <v>206</v>
@@ -5099,12 +5060,12 @@
         <v>328</v>
       </c>
     </row>
-    <row r="106" spans="1:7">
+    <row r="106" spans="1:8">
       <c r="A106" t="s">
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="C106" t="s">
         <v>206</v>
@@ -5119,12 +5080,12 @@
         <v>340</v>
       </c>
     </row>
-    <row r="107" spans="1:7">
+    <row r="107" spans="1:8">
       <c r="A107" t="s">
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>627</v>
+        <v>619</v>
       </c>
       <c r="C107" t="s">
         <v>206</v>
@@ -5139,12 +5100,12 @@
         <v>337</v>
       </c>
     </row>
-    <row r="108" spans="1:7">
+    <row r="108" spans="1:8">
       <c r="A108" t="s">
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="C108" t="s">
         <v>206</v>
@@ -5159,12 +5120,12 @@
         <v>341</v>
       </c>
     </row>
-    <row r="109" spans="1:7">
+    <row r="109" spans="1:8">
       <c r="A109" t="s">
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>629</v>
+        <v>621</v>
       </c>
       <c r="C109" t="s">
         <v>206</v>
@@ -5179,12 +5140,12 @@
         <v>336</v>
       </c>
     </row>
-    <row r="110" spans="1:7">
+    <row r="110" spans="1:8">
       <c r="A110" t="s">
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
       <c r="C110" t="s">
         <v>256</v>
@@ -5196,12 +5157,12 @@
         <v>363</v>
       </c>
     </row>
-    <row r="111" spans="1:7">
+    <row r="111" spans="1:8">
       <c r="A111" t="s">
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="C111" t="s">
         <v>457</v>
@@ -5212,13 +5173,16 @@
       <c r="G111" t="s">
         <v>364</v>
       </c>
-    </row>
-    <row r="112" spans="1:7">
+      <c r="H111" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8">
       <c r="A112" t="s">
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
       <c r="C112" t="s">
         <v>258</v>
@@ -5230,12 +5194,12 @@
         <v>411</v>
       </c>
     </row>
-    <row r="113" spans="1:7">
+    <row r="113" spans="1:8">
       <c r="A113" t="s">
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="C113" t="s">
         <v>257</v>
@@ -5246,13 +5210,16 @@
       <c r="G113" t="s">
         <v>410</v>
       </c>
-    </row>
-    <row r="114" spans="1:7">
+      <c r="H113" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8">
       <c r="A114" t="s">
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="F114" t="s">
         <v>399</v>
@@ -5261,12 +5228,12 @@
         <v>389</v>
       </c>
     </row>
-    <row r="115" spans="1:7">
+    <row r="115" spans="1:8">
       <c r="A115" t="s">
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="F115" t="s">
         <v>400</v>
@@ -5275,12 +5242,12 @@
         <v>390</v>
       </c>
     </row>
-    <row r="116" spans="1:7">
+    <row r="116" spans="1:8">
       <c r="A116" t="s">
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="F116" t="s">
         <v>401</v>
@@ -5289,12 +5256,12 @@
         <v>391</v>
       </c>
     </row>
-    <row r="117" spans="1:7">
+    <row r="117" spans="1:8">
       <c r="A117" t="s">
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="F117" t="s">
         <v>402</v>
@@ -5303,12 +5270,12 @@
         <v>392</v>
       </c>
     </row>
-    <row r="118" spans="1:7">
+    <row r="118" spans="1:8">
       <c r="A118" t="s">
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="F118" t="s">
         <v>403</v>
@@ -5317,12 +5284,12 @@
         <v>393</v>
       </c>
     </row>
-    <row r="119" spans="1:7">
+    <row r="119" spans="1:8">
       <c r="A119" t="s">
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
       <c r="F119" t="s">
         <v>404</v>
@@ -5331,12 +5298,12 @@
         <v>394</v>
       </c>
     </row>
-    <row r="120" spans="1:7">
+    <row r="120" spans="1:8">
       <c r="A120" t="s">
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="F120" t="s">
         <v>405</v>
@@ -5345,12 +5312,12 @@
         <v>397</v>
       </c>
     </row>
-    <row r="121" spans="1:7">
+    <row r="121" spans="1:8">
       <c r="A121" t="s">
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>642</v>
+        <v>634</v>
       </c>
       <c r="F121" t="s">
         <v>406</v>
@@ -5359,12 +5326,12 @@
         <v>395</v>
       </c>
     </row>
-    <row r="122" spans="1:7">
+    <row r="122" spans="1:8">
       <c r="A122" t="s">
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="F122" t="s">
         <v>407</v>
@@ -5373,12 +5340,12 @@
         <v>396</v>
       </c>
     </row>
-    <row r="123" spans="1:7">
+    <row r="123" spans="1:8">
       <c r="A123" t="s">
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="F123" t="s">
         <v>408</v>
@@ -5387,12 +5354,12 @@
         <v>398</v>
       </c>
     </row>
-    <row r="124" spans="1:7">
+    <row r="124" spans="1:8">
       <c r="A124" t="s">
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="F124" t="s">
         <v>250</v>
@@ -5401,12 +5368,12 @@
         <v>388</v>
       </c>
     </row>
-    <row r="125" spans="1:7">
+    <row r="125" spans="1:8">
       <c r="A125" t="s">
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="F125" t="s">
         <v>368</v>
@@ -5415,12 +5382,12 @@
         <v>380</v>
       </c>
     </row>
-    <row r="126" spans="1:7">
+    <row r="126" spans="1:8">
       <c r="A126" t="s">
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>647</v>
+        <v>639</v>
       </c>
       <c r="F126" t="s">
         <v>138</v>
@@ -5429,12 +5396,12 @@
         <v>381</v>
       </c>
     </row>
-    <row r="127" spans="1:7">
+    <row r="127" spans="1:8">
       <c r="A127" t="s">
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>648</v>
+        <v>640</v>
       </c>
       <c r="F127" t="s">
         <v>373</v>
@@ -5443,12 +5410,12 @@
         <v>382</v>
       </c>
     </row>
-    <row r="128" spans="1:7">
+    <row r="128" spans="1:8">
       <c r="A128" t="s">
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>649</v>
+        <v>641</v>
       </c>
       <c r="F128" t="s">
         <v>369</v>
@@ -5462,7 +5429,7 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>650</v>
+        <v>642</v>
       </c>
       <c r="F129" t="s">
         <v>370</v>
@@ -5476,7 +5443,7 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>651</v>
+        <v>643</v>
       </c>
       <c r="F130" t="s">
         <v>374</v>
@@ -5490,7 +5457,7 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>652</v>
+        <v>644</v>
       </c>
       <c r="F131" t="s">
         <v>372</v>
@@ -5504,7 +5471,7 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>653</v>
+        <v>645</v>
       </c>
       <c r="F132" t="s">
         <v>371</v>
@@ -5537,7 +5504,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="C1" t="s">
         <v>140</v>
@@ -5560,7 +5527,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="F2" t="s">
         <v>134</v>
@@ -5574,7 +5541,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="F3" t="s">
         <v>367</v>
@@ -5588,7 +5555,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="F4" t="s">
         <v>135</v>
@@ -5602,7 +5569,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="F5" t="s">
         <v>136</v>
@@ -5616,7 +5583,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="F6" t="s">
         <v>137</v>
@@ -5630,7 +5597,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="C7" t="s">
         <v>141</v>
@@ -5650,7 +5617,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="C8" t="s">
         <v>141</v>
@@ -5670,7 +5637,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="C9" t="s">
         <v>141</v>
@@ -5690,7 +5657,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="C10" t="s">
         <v>141</v>
@@ -5710,7 +5677,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="C11" t="s">
         <v>141</v>
@@ -5730,7 +5697,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="C12" t="s">
         <v>141</v>
@@ -5750,7 +5717,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="C13" t="s">
         <v>141</v>
@@ -5770,7 +5737,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="C14" t="s">
         <v>141</v>
@@ -5790,7 +5757,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="C15" t="s">
         <v>141</v>
@@ -5810,7 +5777,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="C16" t="s">
         <v>142</v>
@@ -5827,7 +5794,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="C17" t="s">
         <v>142</v>
@@ -5844,7 +5811,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="C18" t="s">
         <v>142</v>
@@ -5861,7 +5828,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="C19" t="s">
         <v>142</v>
@@ -5878,7 +5845,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="C20" t="s">
         <v>142</v>
@@ -5895,7 +5862,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="C21" t="s">
         <v>142</v>
@@ -5912,7 +5879,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>538</v>
+        <v>530</v>
       </c>
       <c r="C22" t="s">
         <v>142</v>
@@ -5929,7 +5896,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="C23" t="s">
         <v>142</v>
@@ -5946,7 +5913,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="C24" t="s">
         <v>142</v>
@@ -5966,7 +5933,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="C25" t="s">
         <v>142</v>
@@ -5986,7 +5953,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="C26" t="s">
         <v>142</v>
@@ -6006,7 +5973,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="C27" t="s">
         <v>142</v>
@@ -6026,7 +5993,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="C28" t="s">
         <v>142</v>
@@ -6046,7 +6013,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="C29" t="s">
         <v>142</v>
@@ -6066,7 +6033,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="C30" t="s">
         <v>142</v>
@@ -6086,7 +6053,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="C31" t="s">
         <v>142</v>
@@ -6106,7 +6073,7 @@
         <v>446</v>
       </c>
       <c r="B32" t="s">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="C32" t="s">
         <v>166</v>
@@ -6123,7 +6090,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>549</v>
+        <v>541</v>
       </c>
       <c r="C33" t="s">
         <v>166</v>
@@ -6143,7 +6110,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="C34" t="s">
         <v>166</v>
@@ -6160,7 +6127,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>551</v>
+        <v>543</v>
       </c>
       <c r="C35" t="s">
         <v>166</v>
@@ -6180,7 +6147,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="C36" t="s">
         <v>166</v>
@@ -6197,7 +6164,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>553</v>
+        <v>545</v>
       </c>
       <c r="C37" t="s">
         <v>166</v>
@@ -6217,7 +6184,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="C38" t="s">
         <v>166</v>
@@ -6234,7 +6201,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="C39" t="s">
         <v>166</v>
@@ -6254,7 +6221,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="C40" t="s">
         <v>166</v>
@@ -6271,7 +6238,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="C41" t="s">
         <v>166</v>
@@ -6288,7 +6255,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>558</v>
+        <v>550</v>
       </c>
       <c r="C42" t="s">
         <v>166</v>
@@ -6308,7 +6275,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>559</v>
+        <v>551</v>
       </c>
       <c r="C43" t="s">
         <v>166</v>
@@ -6328,7 +6295,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>560</v>
+        <v>552</v>
       </c>
       <c r="C44" t="s">
         <v>166</v>
@@ -6348,7 +6315,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>561</v>
+        <v>553</v>
       </c>
       <c r="C45" t="s">
         <v>166</v>
@@ -6365,7 +6332,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="C46" t="s">
         <v>166</v>
@@ -6385,7 +6352,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="C47" t="s">
         <v>166</v>
@@ -6405,7 +6372,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="C48" t="s">
         <v>166</v>
@@ -6425,7 +6392,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>565</v>
+        <v>557</v>
       </c>
       <c r="C49" t="s">
         <v>166</v>
@@ -6445,7 +6412,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>566</v>
+        <v>558</v>
       </c>
       <c r="C50" t="s">
         <v>166</v>
@@ -6462,7 +6429,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="C51" t="s">
         <v>166</v>
@@ -6479,7 +6446,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="C52" t="s">
         <v>166</v>
@@ -6499,7 +6466,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="C53" t="s">
         <v>166</v>
@@ -6516,7 +6483,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="C54" t="s">
         <v>166</v>
@@ -6536,7 +6503,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="C55" t="s">
         <v>166</v>
@@ -6556,7 +6523,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>572</v>
+        <v>564</v>
       </c>
       <c r="C56" t="s">
         <v>166</v>
@@ -6573,7 +6540,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="C57" t="s">
         <v>166</v>
@@ -6590,7 +6557,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>574</v>
+        <v>566</v>
       </c>
       <c r="C58" t="s">
         <v>166</v>
@@ -6607,7 +6574,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>575</v>
+        <v>567</v>
       </c>
       <c r="C59" t="s">
         <v>166</v>
@@ -6627,7 +6594,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="C60" t="s">
         <v>166</v>
@@ -6647,7 +6614,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>577</v>
+        <v>569</v>
       </c>
       <c r="C61" t="s">
         <v>166</v>
@@ -6661,10 +6628,10 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="B62" t="s">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="C62" t="s">
         <v>205</v>
@@ -6681,10 +6648,10 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="B63" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="C63" t="s">
         <v>205</v>
@@ -6701,10 +6668,10 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="B64" t="s">
-        <v>580</v>
+        <v>572</v>
       </c>
       <c r="C64" t="s">
         <v>205</v>
@@ -6724,10 +6691,10 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="B65" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="C65" t="s">
         <v>205</v>
@@ -6747,10 +6714,10 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="B66" t="s">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="C66" t="s">
         <v>205</v>
@@ -6767,10 +6734,10 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="B67" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
       <c r="C67" t="s">
         <v>205</v>
@@ -6787,10 +6754,10 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="B68" t="s">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="C68" t="s">
         <v>205</v>
@@ -6810,10 +6777,10 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="B69" t="s">
-        <v>585</v>
+        <v>577</v>
       </c>
       <c r="C69" t="s">
         <v>205</v>
@@ -6836,7 +6803,7 @@
         <v>412</v>
       </c>
       <c r="B70" t="s">
-        <v>654</v>
+        <v>646</v>
       </c>
       <c r="C70" t="s">
         <v>422</v>
@@ -6853,7 +6820,7 @@
         <v>413</v>
       </c>
       <c r="B71" t="s">
-        <v>655</v>
+        <v>647</v>
       </c>
       <c r="C71" t="s">
         <v>422</v>
@@ -6870,7 +6837,7 @@
         <v>414</v>
       </c>
       <c r="B72" t="s">
-        <v>656</v>
+        <v>648</v>
       </c>
       <c r="C72" t="s">
         <v>422</v>
@@ -6887,7 +6854,7 @@
         <v>415</v>
       </c>
       <c r="B73" t="s">
-        <v>657</v>
+        <v>649</v>
       </c>
       <c r="C73" t="s">
         <v>422</v>
@@ -6904,7 +6871,7 @@
         <v>416</v>
       </c>
       <c r="B74" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="C74" t="s">
         <v>422</v>
@@ -6921,7 +6888,7 @@
         <v>417</v>
       </c>
       <c r="B75" t="s">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="C75" t="s">
         <v>422</v>
@@ -6938,7 +6905,7 @@
         <v>418</v>
       </c>
       <c r="B76" t="s">
-        <v>660</v>
+        <v>652</v>
       </c>
       <c r="C76" t="s">
         <v>422</v>
@@ -6955,7 +6922,7 @@
         <v>419</v>
       </c>
       <c r="B77" t="s">
-        <v>661</v>
+        <v>653</v>
       </c>
       <c r="C77" t="s">
         <v>422</v>
@@ -6972,7 +6939,7 @@
         <v>420</v>
       </c>
       <c r="B78" t="s">
-        <v>662</v>
+        <v>654</v>
       </c>
       <c r="C78" t="s">
         <v>422</v>
@@ -6989,7 +6956,7 @@
         <v>421</v>
       </c>
       <c r="B79" t="s">
-        <v>663</v>
+        <v>655</v>
       </c>
       <c r="C79" t="s">
         <v>422</v>
@@ -7006,7 +6973,7 @@
         <v>69</v>
       </c>
       <c r="B80" t="s">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="C80" t="s">
         <v>206</v>
@@ -7026,7 +6993,7 @@
         <v>70</v>
       </c>
       <c r="B81" t="s">
-        <v>621</v>
+        <v>613</v>
       </c>
       <c r="C81" t="s">
         <v>206</v>
@@ -7046,7 +7013,7 @@
         <v>71</v>
       </c>
       <c r="B82" t="s">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="C82" t="s">
         <v>206</v>
@@ -7066,7 +7033,7 @@
         <v>72</v>
       </c>
       <c r="B83" t="s">
-        <v>624</v>
+        <v>616</v>
       </c>
       <c r="C83" t="s">
         <v>206</v>
@@ -7086,7 +7053,7 @@
         <v>73</v>
       </c>
       <c r="B84" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="C84" t="s">
         <v>206</v>
@@ -7106,7 +7073,7 @@
         <v>74</v>
       </c>
       <c r="B85" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="C85" t="s">
         <v>206</v>
@@ -7126,7 +7093,7 @@
         <v>75</v>
       </c>
       <c r="B86" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="C86" t="s">
         <v>206</v>
@@ -7146,7 +7113,7 @@
         <v>76</v>
       </c>
       <c r="B87" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="C87" t="s">
         <v>206</v>
@@ -7166,7 +7133,7 @@
         <v>77</v>
       </c>
       <c r="B88" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="C88" t="s">
         <v>206</v>
@@ -7186,7 +7153,7 @@
         <v>78</v>
       </c>
       <c r="B89" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="C89" t="s">
         <v>206</v>
@@ -7206,7 +7173,7 @@
         <v>79</v>
       </c>
       <c r="B90" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="C90" t="s">
         <v>206</v>
@@ -7226,7 +7193,7 @@
         <v>80</v>
       </c>
       <c r="B91" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="C91" t="s">
         <v>206</v>
@@ -7246,7 +7213,7 @@
         <v>81</v>
       </c>
       <c r="B92" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="C92" t="s">
         <v>206</v>
@@ -7266,7 +7233,7 @@
         <v>82</v>
       </c>
       <c r="B93" t="s">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="C93" t="s">
         <v>206</v>
@@ -7286,7 +7253,7 @@
         <v>83</v>
       </c>
       <c r="B94" t="s">
-        <v>601</v>
+        <v>593</v>
       </c>
       <c r="C94" t="s">
         <v>206</v>
@@ -7306,7 +7273,7 @@
         <v>84</v>
       </c>
       <c r="B95" t="s">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="C95" t="s">
         <v>206</v>
@@ -7326,7 +7293,7 @@
         <v>85</v>
       </c>
       <c r="B96" t="s">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="C96" t="s">
         <v>206</v>
@@ -7346,7 +7313,7 @@
         <v>86</v>
       </c>
       <c r="B97" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="C97" t="s">
         <v>206</v>
@@ -7366,7 +7333,7 @@
         <v>87</v>
       </c>
       <c r="B98" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="C98" t="s">
         <v>206</v>
@@ -7386,7 +7353,7 @@
         <v>88</v>
       </c>
       <c r="B99" t="s">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="C99" t="s">
         <v>206</v>
@@ -7406,7 +7373,7 @@
         <v>447</v>
       </c>
       <c r="B100" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="C100" t="s">
         <v>457</v>
@@ -7423,7 +7390,7 @@
         <v>448</v>
       </c>
       <c r="B101" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
       <c r="C101" t="s">
         <v>256</v>
@@ -7440,7 +7407,7 @@
         <v>111</v>
       </c>
       <c r="B102" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
       <c r="C102" t="s">
         <v>258</v>
@@ -7457,7 +7424,7 @@
         <v>112</v>
       </c>
       <c r="B103" t="s">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="C103" t="s">
         <v>257</v>
@@ -7474,7 +7441,7 @@
         <v>113</v>
       </c>
       <c r="B104" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="F104" t="s">
         <v>399</v>
@@ -7488,7 +7455,7 @@
         <v>114</v>
       </c>
       <c r="B105" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="F105" t="s">
         <v>400</v>
@@ -7502,7 +7469,7 @@
         <v>115</v>
       </c>
       <c r="B106" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="F106" t="s">
         <v>401</v>
@@ -7516,7 +7483,7 @@
         <v>116</v>
       </c>
       <c r="B107" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="F107" t="s">
         <v>402</v>
@@ -7530,7 +7497,7 @@
         <v>117</v>
       </c>
       <c r="B108" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="F108" t="s">
         <v>403</v>
@@ -7544,7 +7511,7 @@
         <v>118</v>
       </c>
       <c r="B109" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
       <c r="F109" t="s">
         <v>404</v>
@@ -7558,7 +7525,7 @@
         <v>119</v>
       </c>
       <c r="B110" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="F110" t="s">
         <v>405</v>
@@ -7572,7 +7539,7 @@
         <v>120</v>
       </c>
       <c r="B111" t="s">
-        <v>642</v>
+        <v>634</v>
       </c>
       <c r="F111" t="s">
         <v>406</v>
@@ -7586,7 +7553,7 @@
         <v>121</v>
       </c>
       <c r="B112" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="F112" t="s">
         <v>407</v>
@@ -7600,7 +7567,7 @@
         <v>122</v>
       </c>
       <c r="B113" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="F113" t="s">
         <v>408</v>
@@ -7611,16 +7578,16 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="B114" t="s">
-        <v>664</v>
+        <v>656</v>
       </c>
       <c r="F114" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="G114" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -7628,7 +7595,7 @@
         <v>123</v>
       </c>
       <c r="B115" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="F115" t="s">
         <v>250</v>
@@ -7642,7 +7609,7 @@
         <v>124</v>
       </c>
       <c r="B116" t="s">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="F116" t="s">
         <v>368</v>
@@ -7656,7 +7623,7 @@
         <v>125</v>
       </c>
       <c r="B117" t="s">
-        <v>647</v>
+        <v>639</v>
       </c>
       <c r="F117" t="s">
         <v>138</v>
@@ -7670,7 +7637,7 @@
         <v>126</v>
       </c>
       <c r="B118" t="s">
-        <v>648</v>
+        <v>640</v>
       </c>
       <c r="F118" t="s">
         <v>373</v>
@@ -7684,7 +7651,7 @@
         <v>127</v>
       </c>
       <c r="B119" t="s">
-        <v>649</v>
+        <v>641</v>
       </c>
       <c r="F119" t="s">
         <v>369</v>
@@ -7698,7 +7665,7 @@
         <v>128</v>
       </c>
       <c r="B120" t="s">
-        <v>650</v>
+        <v>642</v>
       </c>
       <c r="F120" t="s">
         <v>370</v>
@@ -7712,7 +7679,7 @@
         <v>129</v>
       </c>
       <c r="B121" t="s">
-        <v>651</v>
+        <v>643</v>
       </c>
       <c r="F121" t="s">
         <v>374</v>
@@ -7726,7 +7693,7 @@
         <v>130</v>
       </c>
       <c r="B122" t="s">
-        <v>652</v>
+        <v>644</v>
       </c>
       <c r="F122" t="s">
         <v>372</v>
@@ -7740,7 +7707,7 @@
         <v>131</v>
       </c>
       <c r="B123" t="s">
-        <v>653</v>
+        <v>645</v>
       </c>
       <c r="F123" t="s">
         <v>371</v>
@@ -7757,54 +7724,53 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4791DDA-356D-43C5-A405-960C4C715D9E}">
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="18.36328125" customWidth="1"/>
-    <col min="2" max="5" width="15.36328125" customWidth="1"/>
-    <col min="6" max="6" width="27.36328125" customWidth="1"/>
-    <col min="7" max="7" width="26.26953125" customWidth="1"/>
-    <col min="8" max="8" width="13.6328125" customWidth="1"/>
+    <col min="2" max="2" width="15.36328125" customWidth="1"/>
+    <col min="3" max="3" width="33.36328125" customWidth="1"/>
+    <col min="4" max="4" width="26.26953125" customWidth="1"/>
+    <col min="5" max="5" width="26.7265625" customWidth="1"/>
+    <col min="6" max="6" width="26.26953125" customWidth="1"/>
+    <col min="7" max="7" width="21.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>689</v>
+        <v>674</v>
       </c>
       <c r="B1" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="C1" t="s">
-        <v>685</v>
+        <v>140</v>
       </c>
       <c r="D1" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="E1" t="s">
+        <v>675</v>
+      </c>
+      <c r="F1" t="s">
         <v>687</v>
       </c>
-      <c r="F1" t="s">
-        <v>140</v>
-      </c>
       <c r="G1" t="s">
-        <v>495</v>
+        <v>512</v>
       </c>
       <c r="H1" t="s">
-        <v>520</v>
+        <v>251</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="B2" t="s">
-        <v>522</v>
-      </c>
-      <c r="C2" t="s">
-        <v>688</v>
-      </c>
-      <c r="G2" t="s">
-        <v>521</v>
+        <v>514</v>
+      </c>
+      <c r="D2" t="s">
+        <v>513</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -7812,12 +7778,9 @@
         <v>454</v>
       </c>
       <c r="B3" t="s">
-        <v>586</v>
-      </c>
-      <c r="C3" t="s">
-        <v>688</v>
-      </c>
-      <c r="G3" t="s">
+        <v>578</v>
+      </c>
+      <c r="D3" t="s">
         <v>455</v>
       </c>
     </row>
@@ -7828,10 +7791,7 @@
       <c r="B4" t="s">
         <v>456</v>
       </c>
-      <c r="C4" t="s">
-        <v>688</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="D4" t="s">
         <v>457</v>
       </c>
     </row>
@@ -7842,53 +7802,41 @@
       <c r="B5" t="s">
         <v>458</v>
       </c>
-      <c r="C5" t="s">
-        <v>688</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="D5" t="s">
         <v>459</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>665</v>
+        <v>657</v>
       </c>
       <c r="B6" t="s">
-        <v>667</v>
-      </c>
-      <c r="C6" t="s">
-        <v>688</v>
-      </c>
-      <c r="G6" t="s">
-        <v>666</v>
+        <v>659</v>
+      </c>
+      <c r="D6" t="s">
+        <v>658</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="B7" t="s">
-        <v>496</v>
-      </c>
-      <c r="C7" t="s">
-        <v>688</v>
-      </c>
-      <c r="G7" t="s">
-        <v>497</v>
+        <v>490</v>
+      </c>
+      <c r="D7" t="s">
+        <v>491</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="B8" t="s">
-        <v>498</v>
-      </c>
-      <c r="C8" t="s">
-        <v>688</v>
-      </c>
-      <c r="G8" t="s">
-        <v>499</v>
+        <v>492</v>
+      </c>
+      <c r="D8" t="s">
+        <v>493</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -7896,16 +7844,25 @@
         <v>460</v>
       </c>
       <c r="B9" t="s">
-        <v>668</v>
+        <v>660</v>
       </c>
       <c r="C9" t="s">
-        <v>688</v>
+        <v>141</v>
+      </c>
+      <c r="D9" t="s">
+        <v>461</v>
+      </c>
+      <c r="E9" t="s">
+        <v>678</v>
       </c>
       <c r="F9" t="s">
-        <v>141</v>
+        <v>677</v>
       </c>
       <c r="G9" t="s">
-        <v>461</v>
+        <v>698</v>
+      </c>
+      <c r="H9" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -7913,16 +7870,25 @@
         <v>462</v>
       </c>
       <c r="B10" t="s">
-        <v>669</v>
+        <v>661</v>
       </c>
       <c r="C10" t="s">
-        <v>688</v>
+        <v>141</v>
+      </c>
+      <c r="D10" t="s">
+        <v>463</v>
+      </c>
+      <c r="E10" t="s">
+        <v>679</v>
       </c>
       <c r="F10" t="s">
-        <v>141</v>
+        <v>677</v>
       </c>
       <c r="G10" t="s">
-        <v>463</v>
+        <v>698</v>
+      </c>
+      <c r="H10" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -7930,16 +7896,25 @@
         <v>464</v>
       </c>
       <c r="B11" t="s">
-        <v>670</v>
+        <v>662</v>
       </c>
       <c r="C11" t="s">
-        <v>688</v>
+        <v>141</v>
+      </c>
+      <c r="D11" t="s">
+        <v>465</v>
+      </c>
+      <c r="E11" t="s">
+        <v>680</v>
       </c>
       <c r="F11" t="s">
-        <v>141</v>
+        <v>677</v>
       </c>
       <c r="G11" t="s">
-        <v>465</v>
+        <v>698</v>
+      </c>
+      <c r="H11" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -7947,16 +7922,25 @@
         <v>466</v>
       </c>
       <c r="B12" t="s">
-        <v>671</v>
+        <v>663</v>
       </c>
       <c r="C12" t="s">
-        <v>688</v>
+        <v>141</v>
+      </c>
+      <c r="D12" t="s">
+        <v>467</v>
+      </c>
+      <c r="E12" t="s">
+        <v>681</v>
       </c>
       <c r="F12" t="s">
-        <v>141</v>
+        <v>677</v>
       </c>
       <c r="G12" t="s">
-        <v>467</v>
+        <v>698</v>
+      </c>
+      <c r="H12" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -7964,16 +7948,25 @@
         <v>468</v>
       </c>
       <c r="B13" t="s">
-        <v>672</v>
+        <v>664</v>
       </c>
       <c r="C13" t="s">
-        <v>688</v>
+        <v>141</v>
+      </c>
+      <c r="D13" t="s">
+        <v>469</v>
+      </c>
+      <c r="E13" t="s">
+        <v>682</v>
       </c>
       <c r="F13" t="s">
-        <v>141</v>
+        <v>677</v>
       </c>
       <c r="G13" t="s">
-        <v>469</v>
+        <v>698</v>
+      </c>
+      <c r="H13" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -7981,16 +7974,22 @@
         <v>470</v>
       </c>
       <c r="B14" t="s">
-        <v>673</v>
+        <v>665</v>
       </c>
       <c r="C14" t="s">
-        <v>688</v>
-      </c>
-      <c r="F14" t="s">
-        <v>141</v>
+        <v>510</v>
+      </c>
+      <c r="D14" t="s">
+        <v>471</v>
+      </c>
+      <c r="E14" t="s">
+        <v>683</v>
       </c>
       <c r="G14" t="s">
-        <v>471</v>
+        <v>695</v>
+      </c>
+      <c r="H14" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -7998,16 +7997,22 @@
         <v>472</v>
       </c>
       <c r="B15" t="s">
-        <v>674</v>
+        <v>666</v>
       </c>
       <c r="C15" t="s">
-        <v>688</v>
-      </c>
-      <c r="F15" t="s">
-        <v>517</v>
+        <v>510</v>
+      </c>
+      <c r="D15" t="s">
+        <v>473</v>
+      </c>
+      <c r="E15" t="s">
+        <v>684</v>
       </c>
       <c r="G15" t="s">
-        <v>473</v>
+        <v>696</v>
+      </c>
+      <c r="H15" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -8015,331 +8020,157 @@
         <v>474</v>
       </c>
       <c r="B16" t="s">
-        <v>675</v>
+        <v>667</v>
       </c>
       <c r="C16" t="s">
-        <v>688</v>
-      </c>
-      <c r="F16" t="s">
-        <v>517</v>
+        <v>510</v>
+      </c>
+      <c r="D16" t="s">
+        <v>475</v>
+      </c>
+      <c r="E16" t="s">
+        <v>685</v>
       </c>
       <c r="G16" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+        <v>697</v>
+      </c>
+      <c r="H16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
         <v>476</v>
       </c>
       <c r="B17" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="C17" t="s">
-        <v>688</v>
-      </c>
-      <c r="F17" t="s">
-        <v>517</v>
+        <v>699</v>
+      </c>
+      <c r="D17" t="s">
+        <v>477</v>
+      </c>
+      <c r="E17" t="s">
+        <v>686</v>
       </c>
       <c r="G17" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
         <v>478</v>
       </c>
       <c r="B18" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
       <c r="C18" t="s">
+        <v>509</v>
+      </c>
+      <c r="D18" t="s">
+        <v>479</v>
+      </c>
+      <c r="E18" t="s">
         <v>688</v>
       </c>
-      <c r="F18" t="s">
-        <v>517</v>
-      </c>
       <c r="G18" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+        <v>689</v>
+      </c>
+      <c r="H18" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
         <v>480</v>
       </c>
       <c r="B19" t="s">
-        <v>678</v>
+        <v>670</v>
       </c>
       <c r="C19" t="s">
-        <v>688</v>
-      </c>
-      <c r="F19" t="s">
-        <v>517</v>
+        <v>509</v>
+      </c>
+      <c r="D19" t="s">
+        <v>481</v>
+      </c>
+      <c r="E19" t="s">
+        <v>690</v>
       </c>
       <c r="G19" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+        <v>689</v>
+      </c>
+      <c r="H19" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
         <v>482</v>
       </c>
       <c r="B20" t="s">
-        <v>679</v>
+        <v>671</v>
       </c>
       <c r="C20" t="s">
-        <v>688</v>
-      </c>
-      <c r="F20" t="s">
-        <v>515</v>
+        <v>511</v>
+      </c>
+      <c r="D20" t="s">
+        <v>483</v>
+      </c>
+      <c r="E20" t="s">
+        <v>691</v>
       </c>
       <c r="G20" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+        <v>689</v>
+      </c>
+      <c r="H20" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
         <v>484</v>
       </c>
       <c r="B21" t="s">
-        <v>680</v>
+        <v>672</v>
       </c>
       <c r="C21" t="s">
-        <v>688</v>
-      </c>
-      <c r="F21" t="s">
-        <v>516</v>
+        <v>700</v>
+      </c>
+      <c r="D21" t="s">
+        <v>485</v>
+      </c>
+      <c r="E21" t="s">
+        <v>692</v>
       </c>
       <c r="G21" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+        <v>693</v>
+      </c>
+      <c r="H21" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
         <v>486</v>
       </c>
       <c r="B22" t="s">
-        <v>681</v>
+        <v>673</v>
       </c>
       <c r="C22" t="s">
-        <v>688</v>
-      </c>
-      <c r="F22" t="s">
-        <v>516</v>
+        <v>701</v>
+      </c>
+      <c r="D22" t="s">
+        <v>487</v>
+      </c>
+      <c r="E22" t="s">
+        <v>694</v>
       </c>
       <c r="G22" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" t="s">
-        <v>488</v>
-      </c>
-      <c r="B23" t="s">
-        <v>682</v>
-      </c>
-      <c r="C23" t="s">
-        <v>688</v>
-      </c>
-      <c r="F23" t="s">
-        <v>518</v>
-      </c>
-      <c r="G23" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" t="s">
-        <v>490</v>
-      </c>
-      <c r="B24" t="s">
-        <v>683</v>
-      </c>
-      <c r="C24" t="s">
-        <v>688</v>
-      </c>
-      <c r="F24" t="s">
-        <v>519</v>
-      </c>
-      <c r="G24" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" t="s">
-        <v>492</v>
-      </c>
-      <c r="B25" t="s">
-        <v>684</v>
-      </c>
-      <c r="C25" t="s">
-        <v>688</v>
-      </c>
-      <c r="F25" t="s">
-        <v>519</v>
-      </c>
-      <c r="G25" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" t="s">
         <v>693</v>
       </c>
-      <c r="B26" t="s">
-        <v>692</v>
-      </c>
-      <c r="C26" t="s">
-        <v>691</v>
-      </c>
-      <c r="F26" t="s">
-        <v>690</v>
-      </c>
-      <c r="G26" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" t="s">
-        <v>698</v>
-      </c>
-      <c r="B27" t="s">
-        <v>697</v>
-      </c>
-      <c r="C27" t="s">
-        <v>691</v>
-      </c>
-      <c r="F27" t="s">
-        <v>696</v>
-      </c>
-      <c r="G27" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" t="s">
-        <v>699</v>
-      </c>
-      <c r="B28" t="s">
-        <v>700</v>
-      </c>
-      <c r="C28" t="s">
-        <v>691</v>
-      </c>
-      <c r="F28" t="s">
-        <v>701</v>
-      </c>
-      <c r="G28" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" t="s">
-        <v>703</v>
-      </c>
-      <c r="B29" t="s">
-        <v>709</v>
-      </c>
-      <c r="C29" t="s">
-        <v>691</v>
-      </c>
-      <c r="F29" t="s">
-        <v>705</v>
-      </c>
-      <c r="G29" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30" t="s">
-        <v>707</v>
-      </c>
-      <c r="B30" t="s">
-        <v>708</v>
-      </c>
-      <c r="C30" t="s">
-        <v>691</v>
-      </c>
-      <c r="F30" t="s">
-        <v>705</v>
-      </c>
-      <c r="G30" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31" t="s">
-        <v>711</v>
-      </c>
-      <c r="B31" t="s">
-        <v>712</v>
-      </c>
-      <c r="C31" t="s">
-        <v>691</v>
-      </c>
-      <c r="F31" t="s">
-        <v>705</v>
-      </c>
-      <c r="G31" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32" t="s">
-        <v>714</v>
-      </c>
-      <c r="B32" t="s">
-        <v>715</v>
-      </c>
-      <c r="C32" t="s">
-        <v>691</v>
-      </c>
-      <c r="F32" t="s">
-        <v>705</v>
-      </c>
-      <c r="G32" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" t="s">
-        <v>716</v>
-      </c>
-      <c r="B33" t="s">
-        <v>717</v>
-      </c>
-      <c r="F33" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34" t="s">
-        <v>718</v>
-      </c>
-      <c r="B34" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" t="s">
-        <v>720</v>
-      </c>
-      <c r="B35" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" t="s">
-        <v>722</v>
-      </c>
-      <c r="B36" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37" t="s">
-        <v>724</v>
-      </c>
-      <c r="B37" t="s">
-        <v>725</v>
+      <c r="H22" t="s">
+        <v>365</v>
       </c>
     </row>
   </sheetData>
@@ -8350,223 +8181,394 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F70F70F-8AD8-45CB-8C5A-8135C5F9253C}">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="22.08984375" customWidth="1"/>
+    <col min="1" max="1" width="22.36328125" customWidth="1"/>
+    <col min="2" max="2" width="15.36328125" customWidth="1"/>
+    <col min="3" max="3" width="22.08984375" customWidth="1"/>
+    <col min="4" max="4" width="50.90625" customWidth="1"/>
+    <col min="5" max="5" width="36" customWidth="1"/>
+    <col min="7" max="7" width="43.90625" customWidth="1"/>
+    <col min="8" max="8" width="13.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="B1" t="s">
+        <v>489</v>
+      </c>
+      <c r="C1" t="s">
         <v>140</v>
       </c>
-      <c r="C1" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" t="s">
+        <v>676</v>
+      </c>
+      <c r="E1" t="s">
+        <v>675</v>
+      </c>
+      <c r="F1" t="s">
+        <v>687</v>
+      </c>
+      <c r="G1" t="s">
+        <v>512</v>
+      </c>
+      <c r="H1" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>522</v>
-      </c>
-      <c r="C2" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>514</v>
+      </c>
+      <c r="B2" t="s">
+        <v>514</v>
+      </c>
+      <c r="D2" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>454</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B3" t="s">
+        <v>578</v>
+      </c>
+      <c r="D3" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>456</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B4" t="s">
+        <v>456</v>
+      </c>
+      <c r="D4" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>665</v>
-      </c>
-      <c r="C5" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>657</v>
+      </c>
+      <c r="B5" t="s">
+        <v>659</v>
+      </c>
+      <c r="D5" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>458</v>
       </c>
-      <c r="C6" t="s">
+      <c r="B6" t="s">
+        <v>458</v>
+      </c>
+      <c r="D6" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>496</v>
-      </c>
-      <c r="C7" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <v>490</v>
+      </c>
+      <c r="B7" t="s">
+        <v>490</v>
+      </c>
+      <c r="D7" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>498</v>
-      </c>
-      <c r="C8" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+        <v>492</v>
+      </c>
+      <c r="B8" t="s">
+        <v>492</v>
+      </c>
+      <c r="D8" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>460</v>
       </c>
       <c r="B9" t="s">
+        <v>660</v>
+      </c>
+      <c r="C9" t="s">
         <v>141</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>461</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
+      <c r="E9" t="s">
+        <v>678</v>
+      </c>
+      <c r="F9" t="s">
+        <v>677</v>
+      </c>
+      <c r="G9" t="s">
+        <v>698</v>
+      </c>
+      <c r="H9" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>462</v>
       </c>
       <c r="B10" t="s">
+        <v>661</v>
+      </c>
+      <c r="C10" t="s">
         <v>141</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>463</v>
       </c>
-    </row>
-    <row r="11" spans="1:3">
+      <c r="E10" t="s">
+        <v>679</v>
+      </c>
+      <c r="F10" t="s">
+        <v>677</v>
+      </c>
+      <c r="G10" t="s">
+        <v>698</v>
+      </c>
+      <c r="H10" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>464</v>
       </c>
       <c r="B11" t="s">
+        <v>662</v>
+      </c>
+      <c r="C11" t="s">
         <v>141</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>465</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
+      <c r="E11" t="s">
+        <v>680</v>
+      </c>
+      <c r="F11" t="s">
+        <v>677</v>
+      </c>
+      <c r="G11" t="s">
+        <v>698</v>
+      </c>
+      <c r="H11" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>466</v>
       </c>
       <c r="B12" t="s">
+        <v>663</v>
+      </c>
+      <c r="C12" t="s">
         <v>141</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>467</v>
       </c>
-    </row>
-    <row r="13" spans="1:3">
+      <c r="E12" t="s">
+        <v>681</v>
+      </c>
+      <c r="F12" t="s">
+        <v>677</v>
+      </c>
+      <c r="G12" t="s">
+        <v>698</v>
+      </c>
+      <c r="H12" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>468</v>
       </c>
       <c r="B13" t="s">
+        <v>664</v>
+      </c>
+      <c r="C13" t="s">
         <v>141</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>469</v>
       </c>
-    </row>
-    <row r="14" spans="1:3">
+      <c r="E13" t="s">
+        <v>682</v>
+      </c>
+      <c r="F13" t="s">
+        <v>677</v>
+      </c>
+      <c r="G13" t="s">
+        <v>698</v>
+      </c>
+      <c r="H13" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="B14" t="s">
-        <v>515</v>
+        <v>668</v>
       </c>
       <c r="C14" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
+        <v>699</v>
+      </c>
+      <c r="D14" t="s">
+        <v>477</v>
+      </c>
+      <c r="E14" t="s">
+        <v>705</v>
+      </c>
+      <c r="F14" t="s">
+        <v>704</v>
+      </c>
+      <c r="G14" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="B15" t="s">
-        <v>515</v>
+        <v>702</v>
       </c>
       <c r="C15" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
+        <v>699</v>
+      </c>
+      <c r="D15" t="s">
+        <v>497</v>
+      </c>
+      <c r="E15" t="s">
+        <v>706</v>
+      </c>
+      <c r="F15" t="s">
+        <v>704</v>
+      </c>
+      <c r="G15" t="s">
+        <v>689</v>
+      </c>
+      <c r="H15" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>502</v>
+        <v>494</v>
       </c>
       <c r="B16" t="s">
-        <v>515</v>
+        <v>703</v>
       </c>
       <c r="C16" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
+        <v>699</v>
+      </c>
+      <c r="D16" t="s">
+        <v>495</v>
+      </c>
+      <c r="E16" t="s">
+        <v>707</v>
+      </c>
+      <c r="F16" t="s">
+        <v>704</v>
+      </c>
+      <c r="G16" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
+        <v>470</v>
+      </c>
+      <c r="B17" t="s">
+        <v>665</v>
+      </c>
+      <c r="C17" t="s">
+        <v>510</v>
+      </c>
+      <c r="D17" t="s">
+        <v>471</v>
+      </c>
+      <c r="E17" t="s">
+        <v>683</v>
+      </c>
+      <c r="G17" t="s">
+        <v>695</v>
+      </c>
+      <c r="H17" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
         <v>472</v>
       </c>
-      <c r="B17" t="s">
-        <v>517</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="B18" t="s">
+        <v>666</v>
+      </c>
+      <c r="C18" t="s">
+        <v>510</v>
+      </c>
+      <c r="D18" t="s">
         <v>473</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
+      <c r="E18" t="s">
+        <v>684</v>
+      </c>
+      <c r="G18" t="s">
+        <v>696</v>
+      </c>
+      <c r="H18" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
         <v>474</v>
       </c>
-      <c r="B18" t="s">
-        <v>517</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="B19" t="s">
+        <v>667</v>
+      </c>
+      <c r="C19" t="s">
+        <v>510</v>
+      </c>
+      <c r="D19" t="s">
         <v>475</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" t="s">
-        <v>476</v>
-      </c>
-      <c r="B19" t="s">
-        <v>517</v>
-      </c>
-      <c r="C19" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" t="s">
-        <v>480</v>
-      </c>
-      <c r="B20" t="s">
-        <v>517</v>
-      </c>
-      <c r="C20" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" t="s">
-        <v>478</v>
-      </c>
-      <c r="B21" t="s">
-        <v>517</v>
-      </c>
-      <c r="C21" t="s">
-        <v>479</v>
+      <c r="E19" t="s">
+        <v>685</v>
+      </c>
+      <c r="G19" t="s">
+        <v>697</v>
+      </c>
+      <c r="H19" t="s">
+        <v>365</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/0_data/three_challenges_codebook.xlsx
+++ b/0_data/three_challenges_codebook.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Clemens Lindner\Documents\GitHub\bigot_and_tolerant_personalites\0_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8460D08D-A1F1-41E0-A7FE-C45211640101}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37DCE64E-BDB4-495E-8802-753359BD9938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="11440" xr2:uid="{5059903E-ADBB-4520-B1A6-60D4EA1E22CC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{5059903E-ADBB-4520-B1A6-60D4EA1E22CC}"/>
   </bookViews>
   <sheets>
     <sheet name="Study 1a" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1626" uniqueCount="711">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1648" uniqueCount="714">
   <si>
     <t>variable</t>
   </si>
@@ -2638,6 +2638,15 @@
   </si>
   <si>
     <t>1 = isced_1, 2 = isced_2, 3 = isced_2, 4 = isced_3, 5 = isced_4, 6 = isced_6, 7 = isced_7</t>
+  </si>
+  <si>
+    <t>factor</t>
+  </si>
+  <si>
+    <t>numeric</t>
+  </si>
+  <si>
+    <t>var_type</t>
   </si>
 </sst>
 </file>
@@ -7724,19 +7733,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4791DDA-356D-43C5-A405-960C4C715D9E}">
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="18.36328125" customWidth="1"/>
     <col min="2" max="2" width="15.36328125" customWidth="1"/>
     <col min="3" max="3" width="33.36328125" customWidth="1"/>
-    <col min="4" max="4" width="26.26953125" customWidth="1"/>
-    <col min="5" max="5" width="26.7265625" customWidth="1"/>
-    <col min="6" max="6" width="26.26953125" customWidth="1"/>
-    <col min="7" max="7" width="21.7265625" customWidth="1"/>
+    <col min="4" max="4" width="23.1796875" customWidth="1"/>
+    <col min="5" max="5" width="26.26953125" customWidth="1"/>
+    <col min="6" max="6" width="26.7265625" customWidth="1"/>
+    <col min="7" max="7" width="26.26953125" customWidth="1"/>
+    <col min="8" max="8" width="21.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>674</v>
       </c>
@@ -7747,22 +7757,25 @@
         <v>140</v>
       </c>
       <c r="D1" t="s">
+        <v>713</v>
+      </c>
+      <c r="E1" t="s">
         <v>676</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>675</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>687</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>512</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>514</v>
       </c>
@@ -7770,10 +7783,13 @@
         <v>514</v>
       </c>
       <c r="D2" t="s">
+        <v>711</v>
+      </c>
+      <c r="E2" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>454</v>
       </c>
@@ -7781,10 +7797,13 @@
         <v>578</v>
       </c>
       <c r="D3" t="s">
+        <v>712</v>
+      </c>
+      <c r="E3" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
         <v>456</v>
       </c>
@@ -7792,10 +7811,13 @@
         <v>456</v>
       </c>
       <c r="D4" t="s">
+        <v>711</v>
+      </c>
+      <c r="E4" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:9">
       <c r="A5" t="s">
         <v>458</v>
       </c>
@@ -7803,10 +7825,13 @@
         <v>458</v>
       </c>
       <c r="D5" t="s">
+        <v>712</v>
+      </c>
+      <c r="E5" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
         <v>657</v>
       </c>
@@ -7814,10 +7839,13 @@
         <v>659</v>
       </c>
       <c r="D6" t="s">
+        <v>711</v>
+      </c>
+      <c r="E6" t="s">
         <v>658</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:9">
       <c r="A7" t="s">
         <v>490</v>
       </c>
@@ -7825,10 +7853,13 @@
         <v>490</v>
       </c>
       <c r="D7" t="s">
+        <v>711</v>
+      </c>
+      <c r="E7" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
         <v>492</v>
       </c>
@@ -7836,10 +7867,13 @@
         <v>492</v>
       </c>
       <c r="D8" t="s">
+        <v>711</v>
+      </c>
+      <c r="E8" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:9">
       <c r="A9" t="s">
         <v>460</v>
       </c>
@@ -7850,22 +7884,25 @@
         <v>141</v>
       </c>
       <c r="D9" t="s">
+        <v>712</v>
+      </c>
+      <c r="E9" t="s">
         <v>461</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>678</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>677</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>698</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:9">
       <c r="A10" t="s">
         <v>462</v>
       </c>
@@ -7876,22 +7913,25 @@
         <v>141</v>
       </c>
       <c r="D10" t="s">
+        <v>712</v>
+      </c>
+      <c r="E10" t="s">
         <v>463</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>679</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>677</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>698</v>
       </c>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
         <v>464</v>
       </c>
@@ -7902,22 +7942,25 @@
         <v>141</v>
       </c>
       <c r="D11" t="s">
+        <v>712</v>
+      </c>
+      <c r="E11" t="s">
         <v>465</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>680</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>677</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>698</v>
       </c>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:9">
       <c r="A12" t="s">
         <v>466</v>
       </c>
@@ -7928,22 +7971,25 @@
         <v>141</v>
       </c>
       <c r="D12" t="s">
+        <v>712</v>
+      </c>
+      <c r="E12" t="s">
         <v>467</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>681</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>677</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>698</v>
       </c>
-      <c r="H12" t="s">
+      <c r="I12" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:9">
       <c r="A13" t="s">
         <v>468</v>
       </c>
@@ -7954,22 +8000,25 @@
         <v>141</v>
       </c>
       <c r="D13" t="s">
+        <v>712</v>
+      </c>
+      <c r="E13" t="s">
         <v>469</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>682</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>677</v>
       </c>
-      <c r="G13" t="s">
+      <c r="H13" t="s">
         <v>698</v>
       </c>
-      <c r="H13" t="s">
+      <c r="I13" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:9">
       <c r="A14" t="s">
         <v>470</v>
       </c>
@@ -7980,19 +8029,22 @@
         <v>510</v>
       </c>
       <c r="D14" t="s">
+        <v>712</v>
+      </c>
+      <c r="E14" t="s">
         <v>471</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>683</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
         <v>695</v>
       </c>
-      <c r="H14" t="s">
+      <c r="I14" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:9">
       <c r="A15" t="s">
         <v>472</v>
       </c>
@@ -8003,19 +8055,22 @@
         <v>510</v>
       </c>
       <c r="D15" t="s">
+        <v>712</v>
+      </c>
+      <c r="E15" t="s">
         <v>473</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>684</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>696</v>
       </c>
-      <c r="H15" t="s">
+      <c r="I15" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:9">
       <c r="A16" t="s">
         <v>474</v>
       </c>
@@ -8026,19 +8081,22 @@
         <v>510</v>
       </c>
       <c r="D16" t="s">
+        <v>712</v>
+      </c>
+      <c r="E16" t="s">
         <v>475</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>685</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
         <v>697</v>
       </c>
-      <c r="H16" t="s">
+      <c r="I16" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:9">
       <c r="A17" t="s">
         <v>476</v>
       </c>
@@ -8049,16 +8107,19 @@
         <v>699</v>
       </c>
       <c r="D17" t="s">
+        <v>712</v>
+      </c>
+      <c r="E17" t="s">
         <v>477</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>686</v>
       </c>
-      <c r="G17" t="s">
+      <c r="H17" t="s">
         <v>689</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:9">
       <c r="A18" t="s">
         <v>478</v>
       </c>
@@ -8069,19 +8130,22 @@
         <v>509</v>
       </c>
       <c r="D18" t="s">
+        <v>712</v>
+      </c>
+      <c r="E18" t="s">
         <v>479</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>688</v>
       </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
         <v>689</v>
       </c>
-      <c r="H18" t="s">
+      <c r="I18" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:9">
       <c r="A19" t="s">
         <v>480</v>
       </c>
@@ -8092,19 +8156,22 @@
         <v>509</v>
       </c>
       <c r="D19" t="s">
+        <v>712</v>
+      </c>
+      <c r="E19" t="s">
         <v>481</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>690</v>
       </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
         <v>689</v>
       </c>
-      <c r="H19" t="s">
+      <c r="I19" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:9">
       <c r="A20" t="s">
         <v>482</v>
       </c>
@@ -8115,19 +8182,22 @@
         <v>511</v>
       </c>
       <c r="D20" t="s">
+        <v>712</v>
+      </c>
+      <c r="E20" t="s">
         <v>483</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>691</v>
       </c>
-      <c r="G20" t="s">
+      <c r="H20" t="s">
         <v>689</v>
       </c>
-      <c r="H20" t="s">
+      <c r="I20" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:9">
       <c r="A21" t="s">
         <v>484</v>
       </c>
@@ -8138,19 +8208,22 @@
         <v>700</v>
       </c>
       <c r="D21" t="s">
+        <v>712</v>
+      </c>
+      <c r="E21" t="s">
         <v>485</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>692</v>
       </c>
-      <c r="G21" t="s">
+      <c r="H21" t="s">
         <v>693</v>
       </c>
-      <c r="H21" t="s">
+      <c r="I21" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:9">
       <c r="A22" t="s">
         <v>486</v>
       </c>
@@ -8161,15 +8234,18 @@
         <v>701</v>
       </c>
       <c r="D22" t="s">
+        <v>712</v>
+      </c>
+      <c r="E22" t="s">
         <v>487</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>694</v>
       </c>
-      <c r="G22" t="s">
+      <c r="H22" t="s">
         <v>693</v>
       </c>
-      <c r="H22" t="s">
+      <c r="I22" t="s">
         <v>365</v>
       </c>
     </row>
